--- a/Databases/Database3Clean/Winter Birds '14 Clean.xlsx
+++ b/Databases/Database3Clean/Winter Birds '14 Clean.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rohanpoudel/Documents/USFWS/PipingPlover/Databases/Database3Clean/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A511956-6F43-1942-A61A-7B8ACC7F7E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08FFF6D0-82E2-9344-9E55-181A46A67DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4560" yWindow="-21000" windowWidth="38400" windowHeight="20020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-4560" yWindow="-21000" windowWidth="38400" windowHeight="20020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Total Survey Counts" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="327">
   <si>
     <t>Please get a GPS location for individuals and groups of focal species (Snowy Plover SNPL, Piping Plover PIPL, Wilson's Plover WIPL, Red Knot REKN, and American Oystercatcher AMOY) OR Color-banded individuals OR Large aggregations or flocks of birds of 50 or more.  In addition, put your totals for the entire survey route on the "Total Survey Counts" tab.</t>
   </si>
@@ -1009,19 +1009,19 @@
     <t>get time from this</t>
   </si>
   <si>
-    <t>match this with total survey count</t>
-  </si>
-  <si>
-    <t>match it with totoal survey count</t>
-  </si>
-  <si>
-    <t>extract the count of pipl totla it and match it with total survey counts</t>
-  </si>
-  <si>
-    <t>yes keep it</t>
-  </si>
-  <si>
     <t>totla it and compaere with individual flock</t>
+  </si>
+  <si>
+    <t>yess</t>
+  </si>
+  <si>
+    <t>we donot need other species from this text now just PIPL and keep info how many banded or not like this string but remove other species info</t>
+  </si>
+  <si>
+    <t>yes keep it if the band info is about PIPL or looks like it is about pipl</t>
+  </si>
+  <si>
+    <t>Yes keep it</t>
   </si>
 </sst>
 </file>
@@ -1029,8 +1029,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="#,##0.00000"/>
-    <numFmt numFmtId="166" formatCode="m/d/yyyy\ h:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="165" formatCode="m/d/yyyy\ h:mm:ss"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -1148,7 +1148,7 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1157,7 +1157,7 @@
     <xf numFmtId="21" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="21" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1510,7 +1510,7 @@
         <v>321</v>
       </c>
       <c r="K1" s="15" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -3261,11 +3261,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>323</v>
+      </c>
       <c r="E1" s="15" t="s">
-        <v>322</v>
+        <v>15</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>323</v>
+        <v>15</v>
       </c>
       <c r="G1" s="15" t="s">
         <v>324</v>
@@ -3275,6 +3287,9 @@
       </c>
       <c r="I1" s="15" t="s">
         <v>140</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
